--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101009</v>
+        <v>101084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101084</v>
+        <v>101090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101090</v>
+        <v>101091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101091</v>
+        <v>101095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101095</v>
+        <v>101096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101096</v>
+        <v>101098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101098</v>
+        <v>101104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101104</v>
+        <v>101107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57608-2020 artfynd.xlsx
+++ b/artfynd/A 57608-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127127698</v>
       </c>
       <c r="B2" t="n">
-        <v>101107</v>
+        <v>101115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
